--- a/backend/local_storage/daily_work.xlsx
+++ b/backend/local_storage/daily_work.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>project</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>admin_review</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +514,81 @@
           <t>Dadhboard</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10:32 AM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Make A logo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>02:56 PM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Add new features</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
